--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-07-30 / 2026-07-30</t>
+          <t>Ventas 2026-07-31 / 2026-07-31</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>3023.45</v>
+        <v>4371.95</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>312</v>
+        <v>444</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>6768.73</v>
+        <v>7713.08</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>731</v>
+        <v>804</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2710.91</v>
+        <v>2735.36</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>299</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>449.27</v>
+        <v>713.45</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>58</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2061.82</v>
+        <v>2676.73</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>249</v>
+        <v>308</v>
       </c>
     </row>
     <row r="8">
@@ -531,7 +531,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>4051.5</v>
+        <v>4134.05</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1815.95</v>
+        <v>1733.59</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3008.27</v>
+        <v>3073.45</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4133.05</v>
+        <v>4817.26</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>495</v>
+        <v>579</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-07-31 / 2026-07-31</t>
+          <t>Ventas 2026-08-01 / 2026-08-01</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4371.95</v>
+        <v>4490.14</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>444</v>
+        <v>439</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>7713.08</v>
+        <v>8181.59</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>804</v>
+        <v>829</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2735.36</v>
+        <v>3185.59</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>319</v>
+        <v>370</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>713.45</v>
+        <v>991</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>101</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2676.73</v>
+        <v>3504.52</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>308</v>
+        <v>404</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>4134.05</v>
+        <v>4448.32</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>490</v>
+        <v>516</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1733.59</v>
+        <v>1906.32</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>224</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3073.45</v>
+        <v>3691.36</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>322</v>
+        <v>383</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4817.26</v>
+        <v>5167.66</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>579</v>
+        <v>634</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-01 / 2026-08-01</t>
+          <t>Ventas 2026-08-02 / 2026-08-02</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4490.14</v>
+        <v>4156.32</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>439</v>
+        <v>407</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>8181.59</v>
+        <v>7618.8</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>829</v>
+        <v>784</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>3185.59</v>
+        <v>3024.93</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>991</v>
+        <v>540.55</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>127</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>3504.52</v>
+        <v>2917.15</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>404</v>
+        <v>332</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>4448.32</v>
+        <v>3723.05</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>516</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1906.32</v>
+        <v>2126.83</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>243</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3691.36</v>
+        <v>4629.95</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>383</v>
+        <v>444</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>5167.66</v>
+        <v>4866.22</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>634</v>
+        <v>579</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-02 / 2026-08-02</t>
+          <t>Ventas 2026-08-03 / 2026-08-03</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4156.32</v>
+        <v>4020.73</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>407</v>
+        <v>421</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>7618.8</v>
+        <v>7019.64</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>784</v>
+        <v>743</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>3024.93</v>
+        <v>2910.27</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>374</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>540.55</v>
+        <v>597.91</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>74</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2917.15</v>
+        <v>2488.93</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>332</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3723.05</v>
+        <v>3537.07</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>449</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>2126.83</v>
+        <v>1649.09</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>270</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>4629.95</v>
+        <v>4127.64</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>444</v>
+        <v>397</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4866.22</v>
+        <v>4800.35</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>579</v>
+        <v>582</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-03 / 2026-08-03</t>
+          <t>Ventas 2026-08-04 / 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4020.73</v>
+        <v>4577.45</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>421</v>
+        <v>459</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>7019.64</v>
+        <v>6635.92</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>743</v>
+        <v>718</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2910.27</v>
+        <v>2796.91</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>597.91</v>
+        <v>801.8200000000001</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>63</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2488.93</v>
+        <v>2421.55</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3537.07</v>
+        <v>3578.95</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1649.09</v>
+        <v>1606.86</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>206</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>4127.64</v>
+        <v>3777.55</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>397</v>
+        <v>391</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4800.35</v>
+        <v>4436.64</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>582</v>
+        <v>503</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-04 / 2026-08-04</t>
+          <t>Ventas 2026-08-05 / 2026-08-05</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4577.45</v>
+        <v>4232.82</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>459</v>
+        <v>414</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>6635.92</v>
+        <v>6920.86</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>718</v>
+        <v>731</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2796.91</v>
+        <v>2628.73</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>329</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>801.8200000000001</v>
+        <v>806.86</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2421.55</v>
+        <v>2572.34</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3578.95</v>
+        <v>3523.07</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>440</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1606.86</v>
+        <v>1603.25</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>191</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3777.55</v>
+        <v>3625.73</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>391</v>
+        <v>355</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4436.64</v>
+        <v>4723.83</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>503</v>
+        <v>554</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-05 / 2026-08-05</t>
+          <t>Ventas 2026-08-06 / 2026-08-06</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4232.82</v>
+        <v>4306.09</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>6920.86</v>
+        <v>6215.92</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>731</v>
+        <v>691</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2628.73</v>
+        <v>2408.55</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>302</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>806.86</v>
+        <v>609.09</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2572.34</v>
+        <v>2761.15</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>276</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3523.07</v>
+        <v>3816.82</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>433</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1603.25</v>
+        <v>1286.97</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>206</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3625.73</v>
+        <v>3891.18</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>355</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4723.83</v>
+        <v>4755.65</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>554</v>
+        <v>544</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-06 / 2026-08-06</t>
+          <t>Ventas 2026-08-07 / 2026-08-07</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4306.09</v>
+        <v>4325.14</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>6215.92</v>
+        <v>7523.6</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>691</v>
+        <v>827</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2408.55</v>
+        <v>3062.13</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>309</v>
+        <v>351</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>609.09</v>
+        <v>1158</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>90</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2761.15</v>
+        <v>2637.23</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3816.82</v>
+        <v>4214.41</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>445</v>
+        <v>525</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1286.97</v>
+        <v>1648.41</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>169</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3891.18</v>
+        <v>3633.5</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>388</v>
+        <v>357</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4755.65</v>
+        <v>1484.63</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>544</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-07 / 2026-08-07</t>
+          <t>Ventas 2026-08-08 / 2026-08-08</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4325.14</v>
+        <v>5595.14</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>414</v>
+        <v>520</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>7523.6</v>
+        <v>8083.15</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>827</v>
+        <v>862</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>3062.13</v>
+        <v>3117.55</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>351</v>
+        <v>381</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1158</v>
+        <v>1322.18</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2637.23</v>
+        <v>3675.45</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>297</v>
+        <v>404</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>4214.41</v>
+        <v>4405.14</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>525</v>
+        <v>514</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1648.41</v>
+        <v>1959.02</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>207</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3633.5</v>
+        <v>3708.82</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>357</v>
+        <v>375</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>1484.63</v>
+        <v>5694.66</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>171</v>
+        <v>650</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-08 / 2026-08-08</t>
+          <t>Ventas 2026-08-09 / 2026-08-09</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>5595.14</v>
+        <v>5134.32</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>520</v>
+        <v>488</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>8083.15</v>
+        <v>7432.06</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>862</v>
+        <v>819</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>3117.55</v>
+        <v>3307.57</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>381</v>
+        <v>387</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1322.18</v>
+        <v>1080.45</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>149</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>3675.45</v>
+        <v>3252.23</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>404</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>4405.14</v>
+        <v>4073.73</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>514</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1959.02</v>
+        <v>1963.41</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3708.82</v>
+        <v>3851.45</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>375</v>
+        <v>382</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>5694.66</v>
+        <v>4474.08</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>650</v>
+        <v>543</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-09 / 2026-08-09</t>
+          <t>Ventas 2026-08-10 / 2026-08-10</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>5134.32</v>
+        <v>3617.86</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>488</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>7432.06</v>
+        <v>7130.01</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>819</v>
+        <v>756</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>3307.57</v>
+        <v>3064.82</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>387</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1080.45</v>
+        <v>838.86</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>140</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>3252.23</v>
+        <v>2160.04</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>336</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>4073.73</v>
+        <v>3546.74</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>459</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1963.41</v>
+        <v>1228.23</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>234</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3851.45</v>
+        <v>3953.73</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>382</v>
+        <v>393</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4474.08</v>
+        <v>4524.41</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>543</v>
+        <v>570</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-10 / 2026-08-10</t>
+          <t>Ventas 2026-08-11 / 2026-08-11</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>3617.86</v>
+        <v>5431.91</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>354</v>
+        <v>516</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>7130.01</v>
+        <v>6880.82</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>756</v>
+        <v>718</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>3064.82</v>
+        <v>2784.07</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>350</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>838.86</v>
+        <v>829.64</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>118</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2160.04</v>
+        <v>2209.82</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3546.74</v>
+        <v>3673.78</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>415</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1228.23</v>
+        <v>1267.91</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3953.73</v>
+        <v>3759.86</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4524.41</v>
+        <v>4792.76</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>570</v>
+        <v>557</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-11 / 2026-08-11</t>
+          <t>Ventas 2026-08-12 / 2026-08-12</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>5431.91</v>
+        <v>4354.23</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>516</v>
+        <v>421</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>6880.82</v>
+        <v>5920.59</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>718</v>
+        <v>631</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2784.07</v>
+        <v>2276.78</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>345</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>829.64</v>
+        <v>644.23</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>102</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2209.82</v>
+        <v>2038.27</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>260</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3673.78</v>
+        <v>3307.98</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>440</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1267.91</v>
+        <v>1142.33</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>160</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3759.86</v>
+        <v>3311.32</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>397</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4792.76</v>
+        <v>3690.99</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>557</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-12 / 2026-08-12</t>
+          <t>Ventas 2026-08-13 / 2026-08-13</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4354.23</v>
+        <v>4213.77</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>5920.59</v>
+        <v>6941.72</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>631</v>
+        <v>753</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2276.78</v>
+        <v>2311.73</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>644.23</v>
+        <v>907.86</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>75</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2038.27</v>
+        <v>2710.86</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>222</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3307.98</v>
+        <v>3254.77</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1142.33</v>
+        <v>1411.34</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>153</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3311.32</v>
+        <v>3566.73</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>311</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>3690.99</v>
+        <v>5189.16</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>411</v>
+        <v>552</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-13 / 2026-08-13</t>
+          <t>Ventas 2026-08-14 / 2026-08-14</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4213.77</v>
+        <v>4002.68</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>422</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>6941.72</v>
+        <v>3930.64</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>753</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2311.73</v>
+        <v>2606.91</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>281</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>907.86</v>
+        <v>818.36</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2710.86</v>
+        <v>2747.77</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3254.77</v>
+        <v>4625.15</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>382</v>
+        <v>525</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1411.34</v>
+        <v>1300.18</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>185</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3566.73</v>
+        <v>3700</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>342</v>
+        <v>386</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>5189.16</v>
+        <v>5260</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>552</v>
+        <v>593</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-14 / 2026-08-14</t>
+          <t>Ventas 2026-08-15 / 2026-08-15</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4002.68</v>
+        <v>4283.91</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>396</v>
+        <v>442</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>3930.64</v>
+        <v>3485.64</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>420</v>
+        <v>364</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2606.91</v>
+        <v>3056.91</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>307</v>
+        <v>370</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>818.36</v>
+        <v>1124.96</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>96</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2747.77</v>
+        <v>2781.41</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>303</v>
+        <v>313</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>4625.15</v>
+        <v>4487.99</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>525</v>
+        <v>557</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1300.18</v>
+        <v>1904.4</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>163</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3700</v>
+        <v>4138.68</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>386</v>
+        <v>418</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>5260</v>
+        <v>4217.62</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>593</v>
+        <v>494</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-15 / 2026-08-15</t>
+          <t>Ventas 2026-08-16 / 2026-08-16</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4283.91</v>
+        <v>4206.14</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>442</v>
+        <v>428</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>3485.64</v>
+        <v>7536.45</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>364</v>
+        <v>799</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>3056.91</v>
+        <v>2996.74</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>370</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1124.96</v>
+        <v>826.09</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2781.41</v>
+        <v>3531.73</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>313</v>
+        <v>387</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>4487.99</v>
+        <v>3598.18</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>557</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1904.4</v>
+        <v>1913.46</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>229</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>4138.68</v>
+        <v>3773.45</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>418</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4217.62</v>
+        <v>4847.9</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>494</v>
+        <v>589</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-16 / 2026-08-16</t>
+          <t>Ventas 2026-08-17 / 2026-08-17</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4206.14</v>
+        <v>4106.27</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>428</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>7536.45</v>
+        <v>6899.68</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>799</v>
+        <v>712</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2996.74</v>
+        <v>2579.42</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>360</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>826.09</v>
+        <v>729.36</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>3531.73</v>
+        <v>2205.36</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>387</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3598.18</v>
+        <v>2845.49</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>432</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1913.46</v>
+        <v>1446.65</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>246</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3773.45</v>
+        <v>3784.92</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>388</v>
+        <v>399</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4847.9</v>
+        <v>4124.05</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>589</v>
+        <v>527</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-17 / 2026-08-17</t>
+          <t>Ventas 2026-08-18 / 2026-08-18</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4106.27</v>
+        <v>3517.77</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>395</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>6899.68</v>
+        <v>6567.64</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>712</v>
+        <v>697</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2579.42</v>
+        <v>2368.95</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>307</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>729.36</v>
+        <v>662.91</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>93</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2205.36</v>
+        <v>2325.55</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2845.49</v>
+        <v>3589.64</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>374</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1446.65</v>
+        <v>1427.59</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>176</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3784.92</v>
+        <v>3436.82</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>399</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4124.05</v>
+        <v>4728.45</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>527</v>
+        <v>545</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-18 / 2026-08-18</t>
+          <t>Ventas 2026-08-19 / 2026-08-19</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>3517.77</v>
+        <v>4031.86</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>355</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>6567.64</v>
+        <v>6534.41</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>697</v>
+        <v>710</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2368.95</v>
+        <v>2368.05</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>293</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>662.91</v>
+        <v>616.8200000000001</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2325.55</v>
+        <v>2394.45</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3589.64</v>
+        <v>3482.73</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>406</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1427.59</v>
+        <v>1630.24</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>185</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3436.82</v>
+        <v>3817.91</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>356</v>
+        <v>383</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4728.45</v>
+        <v>719.65</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>545</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-19 / 2026-08-19</t>
+          <t>Ventas 2026-08-20 / 2026-08-20</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4031.86</v>
+        <v>4940.09</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>395</v>
+        <v>498</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>6534.41</v>
+        <v>6352.15</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>710</v>
+        <v>700</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2368.05</v>
+        <v>2238.53</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>276</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6">
@@ -499,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>616.8200000000001</v>
+        <v>526.64</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2394.45</v>
+        <v>2000.55</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>250</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3482.73</v>
+        <v>3814.55</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>413</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1630.24</v>
+        <v>1814.36</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>196</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3817.91</v>
+        <v>3294.05</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>383</v>
+        <v>327</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>719.65</v>
+        <v>209.43</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>86</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-20 / 2026-08-20</t>
+          <t>Ventas 2026-08-21 / 2026-08-21</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4940.09</v>
+        <v>4563.27</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>498</v>
+        <v>441</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>6352.15</v>
+        <v>6564.59</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>700</v>
+        <v>720</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2238.53</v>
+        <v>2667.39</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>293</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>526.64</v>
+        <v>717.09</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>70</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2000.55</v>
+        <v>2954.14</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>238</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3814.55</v>
+        <v>4602.79</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>444</v>
+        <v>544</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1814.36</v>
+        <v>1790.78</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3294.05</v>
+        <v>3456.09</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>327</v>
+        <v>351</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>209.43</v>
+        <v>5003.36</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>33</v>
+        <v>577</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-21 / 2026-08-21</t>
+          <t>Ventas 2026-08-22 / 2026-08-22</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4563.27</v>
+        <v>5653.45</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>441</v>
+        <v>522</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>6564.59</v>
+        <v>7778.41</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>720</v>
+        <v>855</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2667.39</v>
+        <v>2884.65</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>319</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>717.09</v>
+        <v>816.36</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2954.14</v>
+        <v>3446</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>326</v>
+        <v>363</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>4602.79</v>
+        <v>4542.65</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1790.78</v>
+        <v>1621.33</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>220</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3456.09</v>
+        <v>4028.64</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>351</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>5003.36</v>
+        <v>5694.31</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>577</v>
+        <v>654</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-22 / 2026-08-22</t>
+          <t>Ventas 2026-08-23 / 2026-08-23</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>5653.45</v>
+        <v>4930.41</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>522</v>
+        <v>496</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>7778.41</v>
+        <v>7224</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>855</v>
+        <v>791</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2884.65</v>
+        <v>2629.55</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>356</v>
+        <v>341</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>816.36</v>
+        <v>773.95</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>3446</v>
+        <v>2762.36</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>363</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>4542.65</v>
+        <v>3716.47</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>543</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1621.33</v>
+        <v>1349.62</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>211</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>4028.64</v>
+        <v>3590.23</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>400</v>
+        <v>367</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>5694.31</v>
+        <v>2819.36</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>654</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-23 / 2026-08-23</t>
+          <t>Ventas 2026-08-24 / 2026-08-24</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4930.41</v>
+        <v>4526.41</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>496</v>
+        <v>435</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>7224</v>
+        <v>6229</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>791</v>
+        <v>657</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2629.55</v>
+        <v>2110.14</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>341</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>773.95</v>
+        <v>399.18</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>98</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2762.36</v>
+        <v>1959.32</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>330</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3716.47</v>
+        <v>3298.77</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>474</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1349.62</v>
+        <v>1468.59</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3590.23</v>
+        <v>2909.55</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>367</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>2819.36</v>
+        <v>4364.81</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>358</v>
+        <v>547</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-24 / 2026-08-24</t>
+          <t>Ventas 2026-08-25 / 2026-08-25</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4526.41</v>
+        <v>3837.09</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>435</v>
+        <v>398</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>6229</v>
+        <v>6151.5</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>657</v>
+        <v>667</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2110.14</v>
+        <v>2330.82</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>263</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>399.18</v>
+        <v>459.09</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1959.32</v>
+        <v>1867.73</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>241</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3298.77</v>
+        <v>3078.05</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>396</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1468.59</v>
+        <v>1310.91</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>181</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>2909.55</v>
+        <v>3305.77</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>313</v>
+        <v>360</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4364.81</v>
+        <v>3999.94</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>547</v>
+        <v>514</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-25 / 2026-08-25</t>
+          <t>Ventas 2026-08-26 / 2026-08-26</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>3837.09</v>
+        <v>3917.95</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>398</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>6151.5</v>
+        <v>6089.33</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>667</v>
+        <v>692</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2330.82</v>
+        <v>2130.36</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>281</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>459.09</v>
+        <v>591.5</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>62</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1867.73</v>
+        <v>2338.73</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>218</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3078.05</v>
+        <v>3341.86</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>374</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1310.91</v>
+        <v>1551.29</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>169</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3305.77</v>
+        <v>2801.36</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>360</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>3999.94</v>
+        <v>4168.03</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>514</v>
+        <v>505</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-26 / 2026-08-26</t>
+          <t>Ventas 2026-08-27 / 2026-08-27</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>3917.95</v>
+        <v>2997.18</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>408</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>6089.33</v>
+        <v>5770.89</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>692</v>
+        <v>662</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2130.36</v>
+        <v>2079.5</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>248</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>591.5</v>
+        <v>738.64</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2338.73</v>
+        <v>2089.78</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>255</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3341.86</v>
+        <v>3322.31</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>412</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1551.29</v>
+        <v>1342.2</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>197</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>2801.36</v>
+        <v>3241.59</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>300</v>
+        <v>333</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4168.03</v>
+        <v>4322.45</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>505</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-27 / 2026-08-27</t>
+          <t>Ventas 2026-08-28 / 2026-08-28</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2997.18</v>
+        <v>4973.55</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>306</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>5770.89</v>
+        <v>6781.75</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>662</v>
+        <v>725</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2079.5</v>
+        <v>2551.23</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>272</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>738.64</v>
+        <v>761.09</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2089.78</v>
+        <v>2991.73</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>239</v>
+        <v>328</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3322.31</v>
+        <v>3383.14</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>405</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1342.2</v>
+        <v>1108.24</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>168</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3241.59</v>
+        <v>2166.95</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>333</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4322.45</v>
+        <v>4999.59</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>519</v>
+        <v>597</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-28 / 2026-08-28</t>
+          <t>Ventas 2026-08-29 / 2026-08-29</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4973.55</v>
+        <v>4080.45</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>501</v>
+        <v>421</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>6781.75</v>
+        <v>7980.45</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>725</v>
+        <v>840</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2551.23</v>
+        <v>2710.52</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>313</v>
+        <v>340</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>761.09</v>
+        <v>711.36</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2991.73</v>
+        <v>4069.5</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>328</v>
+        <v>480</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3383.14</v>
+        <v>3845.28</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>443</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1108.24</v>
+        <v>1785.41</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>143</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>2166.95</v>
+        <v>4087.14</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>228</v>
+        <v>441</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4999.59</v>
+        <v>5306.73</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>597</v>
+        <v>657</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-29 / 2026-08-29</t>
+          <t>Ventas 2026-08-30 / 2026-08-30</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4080.45</v>
+        <v>3844</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>421</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>7980.45</v>
+        <v>6994.49</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>840</v>
+        <v>753</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2710.52</v>
+        <v>2997.65</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>340</v>
+        <v>384</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>711.36</v>
+        <v>501.23</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>95</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>4069.5</v>
+        <v>3664.86</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>480</v>
+        <v>415</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3845.28</v>
+        <v>3308.31</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>458</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1785.41</v>
+        <v>1161.92</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>222</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>4087.14</v>
+        <v>3152.05</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>441</v>
+        <v>371</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>5306.73</v>
+        <v>4241.35</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>657</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-30 / 2026-08-30</t>
+          <t>Ventas 2026-08-31 / 2026-08-31</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>3844</v>
+        <v>2523.09</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>394</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>6994.49</v>
+        <v>5674.77</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>753</v>
+        <v>696</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2997.65</v>
+        <v>1785.14</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>384</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>501.23</v>
+        <v>357.14</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>67</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>3664.86</v>
+        <v>2650.55</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>415</v>
+        <v>308</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3308.31</v>
+        <v>2958.83</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>435</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1161.92</v>
+        <v>878.23</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>152</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3152.05</v>
+        <v>2527.45</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>371</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4241.35</v>
+        <v>3423.83</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>525</v>
+        <v>436</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-08-31 / 2026-08-31</t>
+          <t>Ventas 2026-09-01 / 2026-09-01</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2523.09</v>
+        <v>3280.41</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>282</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>5674.77</v>
+        <v>5255.07</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>696</v>
+        <v>650</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1785.14</v>
+        <v>1579.86</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>251</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>357.14</v>
+        <v>370.45</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2650.55</v>
+        <v>2085.91</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>308</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2958.83</v>
+        <v>2725.88</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>374</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>878.23</v>
+        <v>1061.18</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>120</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>2527.45</v>
+        <v>2394.18</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>299</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>3423.83</v>
+        <v>1886.71</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>436</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-09-01 / 2026-09-01</t>
+          <t>Ventas 2026-09-02 / 2026-09-02</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>3280.41</v>
+        <v>3293.86</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>333</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>5255.07</v>
+        <v>5585.18</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>650</v>
+        <v>681</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1579.86</v>
+        <v>1880.27</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>213</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>370.45</v>
+        <v>536</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2085.91</v>
+        <v>2022.64</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>249</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2725.88</v>
+        <v>2933.38</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>369</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1061.18</v>
+        <v>844.09</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>144</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>2394.18</v>
+        <v>3371.55</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>258</v>
+        <v>372</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>1886.71</v>
+        <v>4269.83</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>241</v>
+        <v>536</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-09-02 / 2026-09-02</t>
+          <t>Ventas 2026-09-03 / 2026-09-03</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>3293.86</v>
+        <v>2916</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>359</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>5585.18</v>
+        <v>5611.36</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>681</v>
+        <v>711</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1880.27</v>
+        <v>1954.23</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>236</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>536</v>
+        <v>557.59</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2022.64</v>
+        <v>2554.14</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>244</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2933.38</v>
+        <v>3212.36</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>406</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>844.09</v>
+        <v>1115.73</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3371.55</v>
+        <v>3564.59</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>372</v>
+        <v>385</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4269.83</v>
+        <v>3660.3</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>536</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-09-03 / 2026-09-03</t>
+          <t>Ventas 2026-09-04 / 2026-09-04</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2916</v>
+        <v>3457.18</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>314</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>5611.36</v>
+        <v>6987.99</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>711</v>
+        <v>822</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1954.23</v>
+        <v>2059.82</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>270</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>557.59</v>
+        <v>995.6799999999999</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>74</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2554.14</v>
+        <v>2537.45</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3212.36</v>
+        <v>3137.09</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>431</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1115.73</v>
+        <v>1000.35</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3564.59</v>
+        <v>3535.82</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>3660.3</v>
+        <v>4307.33</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>481</v>
+        <v>538</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-09-04 / 2026-09-04</t>
+          <t>Ventas 2026-09-05 / 2026-09-05</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>3457.18</v>
+        <v>4463.45</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>374</v>
+        <v>490</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>6987.99</v>
+        <v>7941.01</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>822</v>
+        <v>916</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2059.82</v>
+        <v>2404.32</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>279</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>995.6799999999999</v>
+        <v>1109.73</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>130</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2537.45</v>
+        <v>3541.65</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>301</v>
+        <v>407</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3137.09</v>
+        <v>4096.59</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>391</v>
+        <v>516</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1000.35</v>
+        <v>1521.36</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>139</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3535.82</v>
+        <v>3762.09</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>390</v>
+        <v>409</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4307.33</v>
+        <v>5616.66</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>538</v>
+        <v>657</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-09-05 / 2026-09-05</t>
+          <t>Ventas 2026-09-06 / 2026-09-06</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4463.45</v>
+        <v>3970.95</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>490</v>
+        <v>411</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>7941.01</v>
+        <v>6596.68</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>916</v>
+        <v>762</v>
       </c>
     </row>
     <row r="5">
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2404.32</v>
+        <v>2320.05</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1109.73</v>
+        <v>675.14</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>146</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>3541.65</v>
+        <v>3081.45</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>407</v>
+        <v>366</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>4096.59</v>
+        <v>3075.48</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>516</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1521.36</v>
+        <v>1305.25</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>207</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3762.09</v>
+        <v>4049.23</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>409</v>
+        <v>444</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>5616.66</v>
+        <v>4395.6</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>657</v>
+        <v>568</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-09-06 / 2026-09-06</t>
+          <t>Ventas 2026-09-07 / 2026-09-07</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>3970.95</v>
+        <v>3099.82</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>411</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>6596.68</v>
+        <v>1685.45</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>762</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2320.05</v>
+        <v>1442.09</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>294</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>675.14</v>
+        <v>572.64</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>3081.45</v>
+        <v>1867.82</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>366</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3075.48</v>
+        <v>3137.69</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1305.25</v>
+        <v>921.58</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>169</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>4049.23</v>
+        <v>3414.45</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>444</v>
+        <v>363</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4395.6</v>
+        <v>3524.83</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>568</v>
+        <v>453</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-09-07 / 2026-09-07</t>
+          <t>Ventas 2026-09-08 / 2026-09-08</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>3099.82</v>
+        <v>2781.27</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>340</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>1685.45</v>
+        <v>5490.91</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>208</v>
+        <v>684</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1442.09</v>
+        <v>1595.95</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>202</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>572.64</v>
+        <v>506.27</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1867.82</v>
+        <v>1761.77</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>242</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3137.69</v>
+        <v>3140.17</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>410</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>921.58</v>
+        <v>1067.05</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>124</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3414.45</v>
+        <v>3265.45</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>363</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>3524.83</v>
+        <v>3056.55</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>453</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-09-08 / 2026-09-08</t>
+          <t>Ventas 2026-09-09 / 2026-09-09</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2781.27</v>
+        <v>2271.27</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>294</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>5490.91</v>
+        <v>2511.27</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>684</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1595.95</v>
+        <v>928</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>218</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>506.27</v>
+        <v>501.45</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1761.77</v>
+        <v>1329.45</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>214</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3140.17</v>
+        <v>2882.05</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>395</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1067.05</v>
+        <v>870.17</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3265.45</v>
+        <v>3572.73</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>352</v>
+        <v>392</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>3056.55</v>
+        <v>2621.31</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>420</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-09-09 / 2026-09-09</t>
+          <t>Ventas 2026-09-10 / 2026-09-10</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2271.27</v>
+        <v>3426.09</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>266</v>
+        <v>364</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>2511.27</v>
+        <v>5038.23</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>320</v>
+        <v>639</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>928</v>
+        <v>2017.14</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>130</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>501.45</v>
+        <v>462.73</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1329.45</v>
+        <v>2516.73</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>169</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2882.05</v>
+        <v>2917.5</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>390</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>870.17</v>
+        <v>739.05</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>129</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3572.73</v>
+        <v>2395.36</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>392</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>2621.31</v>
+        <v>4341.3</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>326</v>
+        <v>557</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-09-10 / 2026-09-10</t>
+          <t>Ventas 2026-09-11 / 2026-09-11</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>3426.09</v>
+        <v>3546.59</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>364</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>5038.23</v>
+        <v>7321.5</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>639</v>
+        <v>835</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2017.14</v>
+        <v>3044.45</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>277</v>
+        <v>374</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>462.73</v>
+        <v>826.3200000000001</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>72</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2516.73</v>
+        <v>3017.86</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>305</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2917.5</v>
+        <v>2952.99</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>372</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>739.05</v>
+        <v>988.23</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>115</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>2395.36</v>
+        <v>4796.59</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>244</v>
+        <v>473</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4341.3</v>
+        <v>4337.39</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>557</v>
+        <v>542</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-09-11 / 2026-09-11</t>
+          <t>Ventas 2026-09-12 / 2026-09-12</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>3546.59</v>
+        <v>3780.45</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>399</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>7321.5</v>
+        <v>7518.18</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>835</v>
+        <v>863</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>3044.45</v>
+        <v>2660.5</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>374</v>
+        <v>351</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>826.3200000000001</v>
+        <v>1125.05</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>111</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>3017.86</v>
+        <v>4356.32</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>359</v>
+        <v>499</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2952.99</v>
+        <v>3735.75</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>438</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>988.23</v>
+        <v>1640.63</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>128</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>4796.59</v>
+        <v>3873.45</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>473</v>
+        <v>414</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4337.39</v>
+        <v>5960.1</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>542</v>
+        <v>759</v>
       </c>
     </row>
   </sheetData>
